--- a/config/lecture/lecture_TUM_Sym.xlsx
+++ b/config/lecture/lecture_TUM_Sym.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/config/lecture/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="78" documentId="6_{21B2E60F-E45E-4B1E-BA14-FAE5B07AE4DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F793478F-C88E-4EB9-AA73-051966F51FB2}"/>
+  <xr:revisionPtr revIDLastSave="82" documentId="6_{21B2E60F-E45E-4B1E-BA14-FAE5B07AE4DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C561C10E-D239-43A9-8D48-17989CFE3D65}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="2" r:id="rId1"/>
@@ -1477,10 +1477,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1989,7 +1985,7 @@
         <v>106</v>
       </c>
       <c r="F2" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G2" s="29" t="s">
         <v>16</v>
@@ -2035,7 +2031,7 @@
         <v>49</v>
       </c>
       <c r="F4" s="11">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="G4" s="29" t="s">
         <v>21</v>
@@ -3175,7 +3171,7 @@
         <v>48</v>
       </c>
       <c r="F18" s="9">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G18" s="31" t="s">
         <v>16</v>
@@ -4074,7 +4070,7 @@
         <v>48</v>
       </c>
       <c r="F4" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" s="29" t="s">
         <v>16</v>
